--- a/rules/CORE-000083/negative/02/data/unit-test-coreid-CG0553-negative2.xlsx
+++ b/rules/CORE-000083/negative/02/data/unit-test-coreid-CG0553-negative2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marisa_wyckmans\CORE\CDISC_Rule_Authoring\core-contributor\rules\CORE-000083\negative\02\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8033D1-327F-4295-8DD7-3F31E75D235C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A894206-525A-4E2A-8989-7C96543A9D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="555" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21240" windowHeight="15270" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="94">
   <si>
     <t>Product</t>
   </si>
@@ -314,7 +314,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,6 +338,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -387,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -407,6 +412,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -761,7 +767,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -797,8 +803,11 @@
       <c r="D2">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
-        <v>21</v>
+      <c r="E2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -815,10 +824,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -829,33 +835,36 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="D4">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>92</v>
+      </c>
+      <c r="F5" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -871,11 +880,11 @@
       <c r="D6">
         <v>6</v>
       </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>69</v>
+      <c r="E6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -886,21 +895,18 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -909,30 +915,33 @@
         <v>91</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -943,21 +952,21 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="D10">
         <v>7</v>
       </c>
-      <c r="E10" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" t="s">
-        <v>93</v>
+      <c r="E10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -966,7 +975,7 @@
         <v>91</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
@@ -974,7 +983,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -983,7 +992,7 @@
         <v>91</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -994,7 +1003,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
@@ -1003,12 +1012,89 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
       </c>
       <c r="F13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1295,7 +1381,7 @@
       <c r="D5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>72</v>
       </c>
       <c r="F5" s="6" t="s">
@@ -1350,7 +1436,7 @@
       <c r="D6" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>78</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -1405,7 +1491,7 @@
       <c r="D7" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>82</v>
       </c>
       <c r="F7" s="6" t="s">
@@ -1458,7 +1544,7 @@
       <c r="D8" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>87</v>
       </c>
       <c r="F8" s="6" t="s">
